--- a/Impfquoten/Impfquoten-26.03.2021.xlsx
+++ b/Impfquoten/Impfquoten-26.03.2021.xlsx
@@ -2,22 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9B1E4AB-28F3-4E86-B1F4-ED97E0709D65}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\Pandemie\Impfquoten\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCC45942-B007-4164-BD8E-F41A8FE5503A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="833" yWindow="-98" windowWidth="18465" windowHeight="10996" tabRatio="597" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Erläuterung" sheetId="9" r:id="rId1"/>
-    <sheet name="Gesamt_bis_einschl_26.03.21" sheetId="12" r:id="rId2"/>
-    <sheet name="Indik_bis_einschl_26.03.21" sheetId="11" r:id="rId3"/>
+    <sheet name="Gesamt_bis_einschl_28.03.21" sheetId="12" r:id="rId2"/>
+    <sheet name="Indik_bis_einschl_28.03.21" sheetId="11" r:id="rId3"/>
     <sheet name="Impfungen_proTag" sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Bundesländer001" localSheetId="1">Gesamt_bis_einschl_26.03.21!#REF!</definedName>
-    <definedName name="Bundesländer001" localSheetId="2">Indik_bis_einschl_26.03.21!$G$2:$J$18</definedName>
-    <definedName name="Bundesländer001_1" localSheetId="1">Gesamt_bis_einschl_26.03.21!$D$3:$H$19</definedName>
-    <definedName name="Bundesländer001_1" localSheetId="2">Indik_bis_einschl_26.03.21!$C$2:$F$18</definedName>
+    <definedName name="Bundesländer001" localSheetId="1">Gesamt_bis_einschl_28.03.21!#REF!</definedName>
+    <definedName name="Bundesländer001" localSheetId="2">Indik_bis_einschl_28.03.21!$G$2:$J$18</definedName>
+    <definedName name="Bundesländer001_1" localSheetId="1">Gesamt_bis_einschl_28.03.21!$D$3:$H$19</definedName>
+    <definedName name="Bundesländer001_1" localSheetId="2">Indik_bis_einschl_28.03.21!$C$2:$F$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -235,16 +240,16 @@
     <t>* Impfungen, die in den bundeseigenen Impfzentren aus dem Impfkontingent des Bundes durchgeführt wurden. Diese gehen in die Berechnung der Impfquote für Gesamtdeutschland mit ein und umfassen nur Angehörige des Bundes, die nach §§ 2, 3 und 4 Coronavirus-Impfverordnung geimpft wurden. Die Zahlen werden unregelmäßig aktualisiert (letzte Aktualisierung: 16.03.2021).</t>
   </si>
   <si>
-    <t>Datenstand: 27.03.2021, 8:00 Uhr</t>
-  </si>
-  <si>
-    <t>Durchgeführte Impfungen bundesweit und nach Bundesland bis einschließlich 26.03.21 (Gesamt_bis_einschl_26.03.21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die kumulative Zahl der Impfungen umfasst alle Impfungen, die bis einschließlich 26.03.21 durchgeführt und bis zum 27.03.21, 8:00 Uhr, dem RKI gemeldet wurden. Nachmeldungen und Datenkorrekturen aus zurückliegenden Tagen sind in der kumulativen Zahl der Impfungen enthalten. </t>
-  </si>
-  <si>
-    <t>Anzahl Impfungen nach Indikation bis einschließlich 26.03.21 (Indik_bis_einschl_26.03.21)</t>
+    <t>Datenstand: 29.03.2021, 8:00 Uhr</t>
+  </si>
+  <si>
+    <t>Durchgeführte Impfungen bundesweit und nach Bundesland bis einschließlich 28.03.21 (Gesamt_bis_einschl_28.03.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die kumulative Zahl der Impfungen umfasst alle Impfungen, die bis einschließlich 28.03.21 durchgeführt und bis zum 29.03.21, 8:00 Uhr, dem RKI gemeldet wurden. Nachmeldungen und Datenkorrekturen aus zurückliegenden Tagen sind in der kumulativen Zahl der Impfungen enthalten. </t>
+  </si>
+  <si>
+    <t>Anzahl Impfungen nach Indikation bis einschließlich 28.03.21 (Indik_bis_einschl_28.03.21)</t>
   </si>
   <si>
     <t>-</t>
@@ -1424,43 +1429,43 @@
         <v>1</v>
       </c>
       <c r="C4" s="25">
-        <v>1628665</v>
+        <v>1700817</v>
       </c>
       <c r="D4" s="10">
-        <v>1134891</v>
+        <v>1187818</v>
       </c>
       <c r="E4" s="10">
-        <v>746386</v>
+        <v>767783</v>
       </c>
       <c r="F4" s="10">
-        <v>48949</v>
+        <v>51744</v>
       </c>
       <c r="G4" s="10">
-        <v>339556</v>
+        <v>368291</v>
       </c>
       <c r="H4" s="10">
-        <v>27271</v>
+        <v>23147</v>
       </c>
       <c r="I4" s="24">
-        <v>10.223880341544634</v>
+        <v>10.700683237009425</v>
       </c>
       <c r="J4" s="22">
-        <v>493774</v>
+        <v>512999</v>
       </c>
       <c r="K4" s="10">
-        <v>468295</v>
+        <v>484944</v>
       </c>
       <c r="L4" s="10">
-        <v>25472</v>
+        <v>28047</v>
       </c>
       <c r="M4" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N4" s="11">
-        <v>11380</v>
+        <v>10487</v>
       </c>
       <c r="O4" s="41">
-        <v>4.4482565213450984</v>
+        <v>4.621448572005642</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
@@ -1471,43 +1476,43 @@
         <v>0</v>
       </c>
       <c r="C5" s="26">
-        <v>2071325</v>
+        <v>2140606</v>
       </c>
       <c r="D5" s="15">
-        <v>1416193</v>
+        <v>1469357</v>
       </c>
       <c r="E5" s="15">
-        <v>962622</v>
+        <v>989647</v>
       </c>
       <c r="F5" s="15">
-        <v>72073</v>
+        <v>76820</v>
       </c>
       <c r="G5" s="15">
-        <v>381498</v>
+        <v>402890</v>
       </c>
       <c r="H5" s="16">
-        <v>37758</v>
+        <v>21320</v>
       </c>
       <c r="I5" s="17">
-        <v>10.790258120981777</v>
+        <v>11.195325285375242</v>
       </c>
       <c r="J5" s="23">
-        <v>655132</v>
+        <v>671249</v>
       </c>
       <c r="K5" s="15">
-        <v>634440</v>
+        <v>649371</v>
       </c>
       <c r="L5" s="15">
-        <v>20623</v>
+        <v>21806</v>
       </c>
       <c r="M5" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N5" s="16">
-        <v>11982</v>
+        <v>6356</v>
       </c>
       <c r="O5" s="17">
-        <v>4.9915819265559378</v>
+        <v>5.1143805776831943</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
@@ -1518,43 +1523,43 @@
         <v>3</v>
       </c>
       <c r="C6" s="25">
-        <v>579095</v>
+        <v>607523</v>
       </c>
       <c r="D6" s="10">
-        <v>397207</v>
+        <v>415631</v>
       </c>
       <c r="E6" s="10">
-        <v>266766</v>
+        <v>272771</v>
       </c>
       <c r="F6" s="10">
-        <v>37900</v>
+        <v>39982</v>
       </c>
       <c r="G6" s="10">
-        <v>92541</v>
+        <v>102878</v>
       </c>
       <c r="H6" s="11">
-        <v>11632</v>
+        <v>7263</v>
       </c>
       <c r="I6" s="12">
-        <v>10.824580302826741</v>
+        <v>11.326666286959144</v>
       </c>
       <c r="J6" s="22">
-        <v>181888</v>
+        <v>191892</v>
       </c>
       <c r="K6" s="10">
-        <v>176106</v>
+        <v>185639</v>
       </c>
       <c r="L6" s="10">
-        <v>5782</v>
+        <v>6253</v>
       </c>
       <c r="M6" s="10">
         <v>0</v>
       </c>
       <c r="N6" s="11">
-        <v>5594</v>
+        <v>4928</v>
       </c>
       <c r="O6" s="12">
-        <v>4.9567637582433095</v>
+        <v>5.2293901252244517</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
@@ -1565,43 +1570,43 @@
         <v>2</v>
       </c>
       <c r="C7" s="26">
-        <v>372815</v>
+        <v>390474</v>
       </c>
       <c r="D7" s="15">
-        <v>278745</v>
+        <v>296268</v>
       </c>
       <c r="E7" s="15">
-        <v>174653</v>
+        <v>188373</v>
       </c>
       <c r="F7" s="15">
-        <v>17216</v>
+        <v>18932</v>
       </c>
       <c r="G7" s="15">
-        <v>86876</v>
+        <v>88963</v>
       </c>
       <c r="H7" s="16">
-        <v>5057</v>
+        <v>0</v>
       </c>
       <c r="I7" s="17">
-        <v>11.053006610510439</v>
+        <v>11.747841799790871</v>
       </c>
       <c r="J7" s="23">
-        <v>94070</v>
+        <v>94206</v>
       </c>
       <c r="K7" s="15">
-        <v>89958</v>
+        <v>90093</v>
       </c>
       <c r="L7" s="15">
-        <v>4108</v>
+        <v>4109</v>
       </c>
       <c r="M7" s="15">
         <v>4</v>
       </c>
       <c r="N7" s="16">
-        <v>2156</v>
+        <v>0</v>
       </c>
       <c r="O7" s="17">
-        <v>3.7301344664504006</v>
+        <v>3.735527240846459</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
@@ -1612,31 +1617,31 @@
         <v>4</v>
       </c>
       <c r="C8" s="25">
-        <v>113806</v>
+        <v>118586</v>
       </c>
       <c r="D8" s="10">
-        <v>81020</v>
+        <v>84750</v>
       </c>
       <c r="E8" s="10">
-        <v>52320</v>
+        <v>54560</v>
       </c>
       <c r="F8" s="10">
-        <v>4542</v>
+        <v>5102</v>
       </c>
       <c r="G8" s="10">
-        <v>24158</v>
+        <v>25088</v>
       </c>
       <c r="H8" s="11">
-        <v>2414</v>
+        <v>1423</v>
       </c>
       <c r="I8" s="12">
-        <v>11.893682050258219</v>
+        <v>12.441243566519182</v>
       </c>
       <c r="J8" s="22">
-        <v>32786</v>
+        <v>33836</v>
       </c>
       <c r="K8" s="10">
-        <v>30899</v>
+        <v>31949</v>
       </c>
       <c r="L8" s="10">
         <v>1887</v>
@@ -1645,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="11">
-        <v>698</v>
+        <v>373</v>
       </c>
       <c r="O8" s="12">
-        <v>4.8129629683999751</v>
+        <v>4.9671022692241067</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
@@ -1659,43 +1664,43 @@
         <v>5</v>
       </c>
       <c r="C9" s="26">
-        <v>276740</v>
+        <v>304997</v>
       </c>
       <c r="D9" s="15">
-        <v>191233</v>
+        <v>214835</v>
       </c>
       <c r="E9" s="15">
-        <v>133386</v>
+        <v>152627</v>
       </c>
       <c r="F9" s="15">
-        <v>6996</v>
+        <v>9951</v>
       </c>
       <c r="G9" s="15">
-        <v>50851</v>
+        <v>52257</v>
       </c>
       <c r="H9" s="16">
-        <v>4229</v>
+        <v>4688</v>
       </c>
       <c r="I9" s="17">
-        <v>10.352290671608058</v>
+        <v>11.629971638968781</v>
       </c>
       <c r="J9" s="23">
-        <v>85507</v>
+        <v>90162</v>
       </c>
       <c r="K9" s="15">
-        <v>83893</v>
+        <v>88547</v>
       </c>
       <c r="L9" s="15">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="M9" s="15">
         <v>4</v>
       </c>
       <c r="N9" s="16">
-        <v>1262</v>
+        <v>1061</v>
       </c>
       <c r="O9" s="17">
-        <v>4.6288732512547011</v>
+        <v>4.8808690525878156</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
@@ -1706,43 +1711,43 @@
         <v>15</v>
       </c>
       <c r="C10" s="25">
-        <v>938167</v>
+        <v>977907</v>
       </c>
       <c r="D10" s="10">
-        <v>646444</v>
+        <v>675790</v>
       </c>
       <c r="E10" s="10">
-        <v>446560</v>
+        <v>457295</v>
       </c>
       <c r="F10" s="10">
-        <v>21868</v>
+        <v>23593</v>
       </c>
       <c r="G10" s="10">
-        <v>178016</v>
+        <v>194902</v>
       </c>
       <c r="H10" s="11">
-        <v>14377</v>
+        <v>14056</v>
       </c>
       <c r="I10" s="12">
-        <v>10.280467169628885</v>
+        <v>10.74715970534726</v>
       </c>
       <c r="J10" s="22">
-        <v>291723</v>
+        <v>302117</v>
       </c>
       <c r="K10" s="10">
-        <v>282970</v>
+        <v>292865</v>
       </c>
       <c r="L10" s="10">
-        <v>8683</v>
+        <v>9178</v>
       </c>
       <c r="M10" s="10">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N10" s="11">
-        <v>8198</v>
+        <v>5324</v>
       </c>
       <c r="O10" s="12">
-        <v>4.6393016628287178</v>
+        <v>4.8045985420032826</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
@@ -1753,43 +1758,43 @@
         <v>6</v>
       </c>
       <c r="C11" s="27">
-        <v>226869</v>
+        <v>231783</v>
       </c>
       <c r="D11" s="15">
-        <v>155930</v>
+        <v>160837</v>
       </c>
       <c r="E11" s="15">
-        <v>117928</v>
+        <v>120538</v>
       </c>
       <c r="F11" s="15">
         <v>8742</v>
       </c>
       <c r="G11" s="15">
-        <v>29260</v>
+        <v>31557</v>
       </c>
       <c r="H11" s="16">
-        <v>6623</v>
+        <v>856</v>
       </c>
       <c r="I11" s="17">
-        <v>9.6963071577190512</v>
+        <v>10.001442662259084</v>
       </c>
       <c r="J11" s="23">
-        <v>70939</v>
+        <v>70946</v>
       </c>
       <c r="K11" s="15">
-        <v>67925</v>
+        <v>67930</v>
       </c>
       <c r="L11" s="15">
         <v>2965</v>
       </c>
       <c r="M11" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N11" s="16">
-        <v>1226</v>
+        <v>2</v>
       </c>
       <c r="O11" s="17">
-        <v>4.4112507757418831</v>
+        <v>4.4116860617683304</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
@@ -1800,43 +1805,43 @@
         <v>7</v>
       </c>
       <c r="C12" s="25">
-        <v>1190115</v>
+        <v>1224348</v>
       </c>
       <c r="D12" s="10">
-        <v>816673</v>
+        <v>846349</v>
       </c>
       <c r="E12" s="10">
-        <v>540525</v>
+        <v>549838</v>
       </c>
       <c r="F12" s="10">
-        <v>37333</v>
+        <v>40488</v>
       </c>
       <c r="G12" s="10">
-        <v>238815</v>
+        <v>256023</v>
       </c>
       <c r="H12" s="11">
-        <v>27439</v>
+        <v>6325</v>
       </c>
       <c r="I12" s="12">
-        <v>10.216575543859543</v>
+        <v>10.587822169913762</v>
       </c>
       <c r="J12" s="22">
-        <v>373442</v>
+        <v>377999</v>
       </c>
       <c r="K12" s="10">
-        <v>363418</v>
+        <v>367733</v>
       </c>
       <c r="L12" s="10">
-        <v>10023</v>
+        <v>10265</v>
       </c>
       <c r="M12" s="10">
         <v>1</v>
       </c>
       <c r="N12" s="11">
-        <v>11679</v>
+        <v>457</v>
       </c>
       <c r="O12" s="12">
-        <v>4.6717577344298089</v>
+        <v>4.7287657838613049</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
@@ -1847,43 +1852,43 @@
         <v>8</v>
       </c>
       <c r="C13" s="26">
-        <v>2453526</v>
+        <v>2576687</v>
       </c>
       <c r="D13" s="15">
-        <v>1707930</v>
+        <v>1803565</v>
       </c>
       <c r="E13" s="15">
-        <v>1167944</v>
+        <v>1162820</v>
       </c>
       <c r="F13" s="15">
-        <v>42392</v>
+        <v>52180</v>
       </c>
       <c r="G13" s="15">
-        <v>497594</v>
+        <v>588565</v>
       </c>
       <c r="H13" s="16">
-        <v>25259</v>
+        <v>15384</v>
       </c>
       <c r="I13" s="17">
-        <v>9.5164036816619131</v>
+        <v>10.049271695044041</v>
       </c>
       <c r="J13" s="23">
-        <v>745596</v>
+        <v>773122</v>
       </c>
       <c r="K13" s="15">
-        <v>731595</v>
+        <v>753388</v>
       </c>
       <c r="L13" s="15">
-        <v>13690</v>
+        <v>19348</v>
       </c>
       <c r="M13" s="15">
-        <v>311</v>
+        <v>386</v>
       </c>
       <c r="N13" s="16">
-        <v>15292</v>
+        <v>8984</v>
       </c>
       <c r="O13" s="17">
-        <v>4.1543813384813166</v>
+        <v>4.3077532727768828</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
@@ -1894,31 +1899,31 @@
         <v>12</v>
       </c>
       <c r="C14" s="25">
-        <v>646422</v>
+        <v>654568</v>
       </c>
       <c r="D14" s="10">
-        <v>470688</v>
+        <v>478818</v>
       </c>
       <c r="E14" s="10">
-        <v>314022</v>
+        <v>320476</v>
       </c>
       <c r="F14" s="10">
-        <v>26188</v>
+        <v>27192</v>
       </c>
       <c r="G14" s="10">
-        <v>130478</v>
+        <v>131150</v>
       </c>
       <c r="H14" s="11">
-        <v>12177</v>
+        <v>2243</v>
       </c>
       <c r="I14" s="12">
-        <v>11.497292437070444</v>
+        <v>11.695880434880845</v>
       </c>
       <c r="J14" s="22">
-        <v>175734</v>
+        <v>175750</v>
       </c>
       <c r="K14" s="10">
-        <v>170886</v>
+        <v>170902</v>
       </c>
       <c r="L14" s="10">
         <v>4799</v>
@@ -1927,10 +1932,10 @@
         <v>49</v>
       </c>
       <c r="N14" s="11">
-        <v>1055</v>
+        <v>0</v>
       </c>
       <c r="O14" s="12">
-        <v>4.2925785002722341</v>
+        <v>4.2929693253601755</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
@@ -1941,43 +1946,43 @@
         <v>13</v>
       </c>
       <c r="C15" s="26">
-        <v>162453</v>
+        <v>165991</v>
       </c>
       <c r="D15" s="15">
-        <v>121858</v>
+        <v>124583</v>
       </c>
       <c r="E15" s="15">
-        <v>81048</v>
+        <v>82197</v>
       </c>
       <c r="F15" s="15">
-        <v>6584</v>
+        <v>6829</v>
       </c>
       <c r="G15" s="15">
-        <v>34226</v>
+        <v>35557</v>
       </c>
       <c r="H15" s="16">
-        <v>3249</v>
+        <v>0</v>
       </c>
       <c r="I15" s="17">
-        <v>12.347715594591884</v>
+        <v>12.623836366270909</v>
       </c>
       <c r="J15" s="23">
-        <v>40595</v>
+        <v>41408</v>
       </c>
       <c r="K15" s="15">
-        <v>39129</v>
+        <v>39938</v>
       </c>
       <c r="L15" s="15">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="M15" s="15">
         <v>4</v>
       </c>
       <c r="N15" s="16">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="O15" s="17">
-        <v>4.1134395325908635</v>
+        <v>4.1958197848385881</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
@@ -1988,43 +1993,43 @@
         <v>9</v>
       </c>
       <c r="C16" s="25">
-        <v>580493</v>
+        <v>609713</v>
       </c>
       <c r="D16" s="10">
-        <v>363806</v>
+        <v>382309</v>
       </c>
       <c r="E16" s="10">
-        <v>279793</v>
+        <v>288608</v>
       </c>
       <c r="F16" s="10">
-        <v>18704</v>
+        <v>20567</v>
       </c>
       <c r="G16" s="10">
-        <v>65309</v>
+        <v>73134</v>
       </c>
       <c r="H16" s="11">
-        <v>10599</v>
+        <v>8395</v>
       </c>
       <c r="I16" s="12">
-        <v>8.9343956526212978</v>
+        <v>9.3887947630275352</v>
       </c>
       <c r="J16" s="22">
-        <v>216687</v>
+        <v>227404</v>
       </c>
       <c r="K16" s="10">
-        <v>208412</v>
+        <v>218315</v>
       </c>
       <c r="L16" s="10">
-        <v>8275</v>
+        <v>9089</v>
       </c>
       <c r="M16" s="10">
         <v>0</v>
       </c>
       <c r="N16" s="11">
-        <v>5930</v>
+        <v>5141</v>
       </c>
       <c r="O16" s="12">
-        <v>5.3214278785384277</v>
+        <v>5.5846173757131377</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.45">
@@ -2035,43 +2040,43 @@
         <v>10</v>
       </c>
       <c r="C17" s="26">
-        <v>315919</v>
+        <v>325610</v>
       </c>
       <c r="D17" s="15">
-        <v>227201</v>
+        <v>235323</v>
       </c>
       <c r="E17" s="15">
-        <v>151672</v>
+        <v>154677</v>
       </c>
       <c r="F17" s="15">
-        <v>15058</v>
+        <v>15365</v>
       </c>
       <c r="G17" s="15">
-        <v>60471</v>
+        <v>65281</v>
       </c>
       <c r="H17" s="16">
-        <v>5196</v>
+        <v>2423</v>
       </c>
       <c r="I17" s="17">
-        <v>10.351870937523636</v>
+        <v>10.721930469632063</v>
       </c>
       <c r="J17" s="23">
-        <v>88718</v>
+        <v>90287</v>
       </c>
       <c r="K17" s="15">
-        <v>84858</v>
+        <v>86128</v>
       </c>
       <c r="L17" s="15">
-        <v>3855</v>
+        <v>4154</v>
       </c>
       <c r="M17" s="15">
         <v>5</v>
       </c>
       <c r="N17" s="16">
-        <v>1791</v>
+        <v>117</v>
       </c>
       <c r="O17" s="17">
-        <v>4.0422237835010488</v>
+        <v>4.1137115212353663</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.45">
@@ -2082,43 +2087,43 @@
         <v>11</v>
       </c>
       <c r="C18" s="25">
-        <v>447089</v>
+        <v>465819</v>
       </c>
       <c r="D18" s="10">
-        <v>339119</v>
+        <v>355289</v>
       </c>
       <c r="E18" s="10">
-        <v>228043</v>
+        <v>236826</v>
       </c>
       <c r="F18" s="10">
-        <v>17723</v>
+        <v>18990</v>
       </c>
       <c r="G18" s="10">
-        <v>93353</v>
+        <v>99473</v>
       </c>
       <c r="H18" s="11">
-        <v>8425</v>
+        <v>7417</v>
       </c>
       <c r="I18" s="12">
-        <v>11.678564405688736</v>
+        <v>12.235426116297658</v>
       </c>
       <c r="J18" s="22">
-        <v>107970</v>
+        <v>110530</v>
       </c>
       <c r="K18" s="10">
-        <v>104856</v>
+        <v>107213</v>
       </c>
       <c r="L18" s="10">
-        <v>3072</v>
+        <v>3263</v>
       </c>
       <c r="M18" s="10">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="N18" s="11">
-        <v>1226</v>
+        <v>1204</v>
       </c>
       <c r="O18" s="12">
-        <v>3.7182658561809063</v>
+        <v>3.8064270175389057</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.45">
@@ -2129,43 +2134,43 @@
         <v>14</v>
       </c>
       <c r="C19" s="26">
-        <v>359940</v>
+        <v>377430</v>
       </c>
       <c r="D19" s="15">
-        <v>246441</v>
+        <v>263443</v>
       </c>
       <c r="E19" s="15">
-        <v>163932</v>
+        <v>164459</v>
       </c>
       <c r="F19" s="15">
-        <v>8988</v>
+        <v>19974</v>
       </c>
       <c r="G19" s="15">
-        <v>73521</v>
+        <v>79010</v>
       </c>
       <c r="H19" s="16">
-        <v>5904</v>
+        <v>8230</v>
       </c>
       <c r="I19" s="17">
-        <v>11.551680011699755</v>
+        <v>12.348632075515919</v>
       </c>
       <c r="J19" s="23">
-        <v>113499</v>
+        <v>113987</v>
       </c>
       <c r="K19" s="15">
-        <v>105822</v>
+        <v>106297</v>
       </c>
       <c r="L19" s="15">
-        <v>7647</v>
+        <v>7660</v>
       </c>
       <c r="M19" s="15">
         <v>30</v>
       </c>
       <c r="N19" s="16">
-        <v>2724</v>
+        <v>88</v>
       </c>
       <c r="O19" s="17">
-        <v>5.3201542342707198</v>
+        <v>5.3430287553354345</v>
       </c>
       <c r="P19" s="53"/>
       <c r="Q19" s="53"/>
@@ -2225,43 +2230,43 @@
         <v>19</v>
       </c>
       <c r="C21" s="44">
-        <v>12370419</v>
+        <v>12879839</v>
       </c>
       <c r="D21" s="42">
-        <v>8602339</v>
+        <v>9001925</v>
       </c>
       <c r="E21" s="42">
-        <v>5827600</v>
+        <v>5963495</v>
       </c>
       <c r="F21" s="42">
-        <v>391626</v>
+        <v>436821</v>
       </c>
       <c r="G21" s="42">
-        <v>2383113</v>
+        <v>2601609</v>
       </c>
       <c r="H21" s="42">
-        <v>207609</v>
+        <v>123170</v>
       </c>
       <c r="I21" s="45">
-        <v>10.343488273811861</v>
+        <v>10.823952145949358</v>
       </c>
       <c r="J21" s="46">
-        <v>3768080</v>
+        <v>3877914</v>
       </c>
       <c r="K21" s="42">
-        <v>3643462</v>
+        <v>3741252</v>
       </c>
       <c r="L21" s="42">
-        <v>123973</v>
+        <v>135920</v>
       </c>
       <c r="M21" s="42">
-        <v>645</v>
+        <v>742</v>
       </c>
       <c r="N21" s="42">
-        <v>83022</v>
+        <v>44522</v>
       </c>
       <c r="O21" s="45">
-        <v>4.5307550998379629</v>
+        <v>4.6628199592983783</v>
       </c>
       <c r="P21" s="53"/>
       <c r="Q21" s="53"/>
@@ -2397,28 +2402,28 @@
         <v>1</v>
       </c>
       <c r="C3" s="13">
-        <v>516041</v>
+        <v>539160</v>
       </c>
       <c r="D3" s="11">
-        <v>473932</v>
+        <v>489928</v>
       </c>
       <c r="E3" s="11">
-        <v>86207</v>
+        <v>96472</v>
       </c>
       <c r="F3" s="14">
-        <v>99260</v>
+        <v>100302</v>
       </c>
       <c r="G3" s="13">
-        <v>313408</v>
+        <v>329243</v>
       </c>
       <c r="H3" s="11">
-        <v>148991</v>
+        <v>151250</v>
       </c>
       <c r="I3" s="11">
-        <v>10094</v>
+        <v>10721</v>
       </c>
       <c r="J3" s="14">
-        <v>81045</v>
+        <v>81966</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
@@ -2429,28 +2434,28 @@
         <v>0</v>
       </c>
       <c r="C4" s="19">
-        <v>665653</v>
+        <v>693618</v>
       </c>
       <c r="D4" s="16">
-        <v>586026</v>
+        <v>603193</v>
       </c>
       <c r="E4" s="16">
-        <v>126491</v>
+        <v>137733</v>
       </c>
       <c r="F4" s="18">
-        <v>137928</v>
+        <v>138541</v>
       </c>
       <c r="G4" s="19">
-        <v>327357</v>
+        <v>340377</v>
       </c>
       <c r="H4" s="16">
-        <v>254184</v>
+        <v>256491</v>
       </c>
       <c r="I4" s="16">
-        <v>21034</v>
+        <v>22227</v>
       </c>
       <c r="J4" s="18">
-        <v>112312</v>
+        <v>113068</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
@@ -2461,28 +2466,28 @@
         <v>3</v>
       </c>
       <c r="C5" s="13">
-        <v>273338</v>
+        <v>284490</v>
       </c>
       <c r="D5" s="11">
-        <v>128348</v>
+        <v>134923</v>
       </c>
       <c r="E5" s="11">
-        <v>5634</v>
+        <v>7826</v>
       </c>
       <c r="F5" s="14">
-        <v>48497</v>
+        <v>49164</v>
       </c>
       <c r="G5" s="13">
-        <v>142476</v>
+        <v>151103</v>
       </c>
       <c r="H5" s="11">
-        <v>39259</v>
+        <v>40903</v>
       </c>
       <c r="I5" s="11">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="J5" s="14">
-        <v>41219</v>
+        <v>41361</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
@@ -2493,22 +2498,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="19">
-        <v>138584</v>
+        <v>145597</v>
       </c>
       <c r="D6" s="16">
-        <v>106291</v>
+        <v>107277</v>
       </c>
       <c r="E6" s="16">
-        <v>32537</v>
+        <v>34020</v>
       </c>
       <c r="F6" s="18">
-        <v>27028</v>
+        <v>27046</v>
       </c>
       <c r="G6" s="19">
-        <v>48362</v>
+        <v>48477</v>
       </c>
       <c r="H6" s="16">
-        <v>43021</v>
+        <v>43042</v>
       </c>
       <c r="I6" s="16">
         <v>1666</v>
@@ -2525,28 +2530,28 @@
         <v>4</v>
       </c>
       <c r="C7" s="13">
-        <v>35939</v>
+        <v>38919</v>
       </c>
       <c r="D7" s="11">
-        <v>39042</v>
+        <v>39531</v>
       </c>
       <c r="E7" s="11">
-        <v>1937</v>
+        <v>2141</v>
       </c>
       <c r="F7" s="14">
-        <v>8798</v>
+        <v>8843</v>
       </c>
       <c r="G7" s="13">
-        <v>17567</v>
+        <v>18406</v>
       </c>
       <c r="H7" s="11">
-        <v>11775</v>
+        <v>11921</v>
       </c>
       <c r="I7" s="11">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="J7" s="14">
-        <v>7282</v>
+        <v>7403</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
@@ -2557,28 +2562,28 @@
         <v>5</v>
       </c>
       <c r="C8" s="19">
-        <v>73840</v>
+        <v>79268</v>
       </c>
       <c r="D8" s="16">
-        <v>104664</v>
+        <v>120468</v>
       </c>
       <c r="E8" s="16">
-        <v>7511</v>
+        <v>9742</v>
       </c>
       <c r="F8" s="18">
-        <v>16043</v>
+        <v>16049</v>
       </c>
       <c r="G8" s="19">
-        <v>45767</v>
+        <v>49870</v>
       </c>
       <c r="H8" s="16">
-        <v>35759</v>
+        <v>36266</v>
       </c>
       <c r="I8" s="16">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="J8" s="18">
-        <v>13243</v>
+        <v>13320</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
@@ -2589,28 +2594,28 @@
         <v>15</v>
       </c>
       <c r="C9" s="13">
-        <v>257676</v>
+        <v>262805</v>
       </c>
       <c r="D9" s="11">
-        <v>255668</v>
+        <v>267900</v>
       </c>
       <c r="E9" s="11">
-        <v>56537</v>
+        <v>58044</v>
       </c>
       <c r="F9" s="14">
-        <v>55400</v>
+        <v>55620</v>
       </c>
       <c r="G9" s="13">
-        <v>171661</v>
+        <v>179071</v>
       </c>
       <c r="H9" s="11">
-        <v>97139</v>
+        <v>99316</v>
       </c>
       <c r="I9" s="11">
-        <v>14772</v>
+        <v>15538</v>
       </c>
       <c r="J9" s="14">
-        <v>41107</v>
+        <v>41168</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
@@ -2621,22 +2626,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="19">
-        <v>63945</v>
+        <v>66207</v>
       </c>
       <c r="D10" s="16">
-        <v>59891</v>
+        <v>62129</v>
       </c>
       <c r="E10" s="16">
-        <v>7287</v>
+        <v>7706</v>
       </c>
       <c r="F10" s="18">
-        <v>29432</v>
+        <v>29462</v>
       </c>
       <c r="G10" s="19">
-        <v>25416</v>
+        <v>25417</v>
       </c>
       <c r="H10" s="16">
-        <v>28328</v>
+        <v>28334</v>
       </c>
       <c r="I10" s="16">
         <v>1004</v>
@@ -2653,28 +2658,28 @@
         <v>7</v>
       </c>
       <c r="C11" s="13">
-        <v>395051</v>
+        <v>409408</v>
       </c>
       <c r="D11" s="11">
-        <v>340174</v>
+        <v>354847</v>
       </c>
       <c r="E11" s="11">
-        <v>67627</v>
+        <v>69999</v>
       </c>
       <c r="F11" s="14">
-        <v>106045</v>
+        <v>106705</v>
       </c>
       <c r="G11" s="13">
-        <v>211995</v>
+        <v>216045</v>
       </c>
       <c r="H11" s="11">
-        <v>109191</v>
+        <v>109665</v>
       </c>
       <c r="I11" s="11">
-        <v>34776</v>
+        <v>35389</v>
       </c>
       <c r="J11" s="14">
-        <v>86956</v>
+        <v>86991</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -2685,28 +2690,28 @@
         <v>8</v>
       </c>
       <c r="C12" s="19">
-        <v>662334</v>
+        <v>729974</v>
       </c>
       <c r="D12" s="16">
-        <v>888439</v>
+        <v>951479</v>
       </c>
       <c r="E12" s="16">
-        <v>39738</v>
+        <v>53451</v>
       </c>
       <c r="F12" s="18">
-        <v>203707</v>
+        <v>196443</v>
       </c>
       <c r="G12" s="19">
-        <v>317170</v>
+        <v>382876</v>
       </c>
       <c r="H12" s="16">
-        <v>328924</v>
+        <v>325413</v>
       </c>
       <c r="I12" s="16">
-        <v>16892</v>
+        <v>19942</v>
       </c>
       <c r="J12" s="18">
-        <v>154629</v>
+        <v>151671</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
@@ -2717,22 +2722,22 @@
         <v>12</v>
       </c>
       <c r="C13" s="13">
-        <v>206103</v>
+        <v>208698</v>
       </c>
       <c r="D13" s="11">
-        <v>215993</v>
+        <v>218454</v>
       </c>
       <c r="E13" s="11">
-        <v>18618</v>
+        <v>20235</v>
       </c>
       <c r="F13" s="14">
-        <v>47565</v>
+        <v>47646</v>
       </c>
       <c r="G13" s="13">
-        <v>104544</v>
+        <v>104558</v>
       </c>
       <c r="H13" s="11">
-        <v>60866</v>
+        <v>60868</v>
       </c>
       <c r="I13" s="11">
         <v>714</v>
@@ -2749,28 +2754,28 @@
         <v>13</v>
       </c>
       <c r="C14" s="19">
-        <v>62638</v>
+        <v>63946</v>
       </c>
       <c r="D14" s="16">
-        <v>42807</v>
+        <v>43498</v>
       </c>
       <c r="E14" s="16">
-        <v>8236</v>
+        <v>8850</v>
       </c>
       <c r="F14" s="18">
-        <v>14663</v>
+        <v>14787</v>
       </c>
       <c r="G14" s="19">
-        <v>27647</v>
+        <v>28332</v>
       </c>
       <c r="H14" s="16">
-        <v>9468</v>
+        <v>9564</v>
       </c>
       <c r="I14" s="16">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J14" s="18">
-        <v>9687</v>
+        <v>9724</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
@@ -2781,28 +2786,28 @@
         <v>9</v>
       </c>
       <c r="C15" s="13">
-        <v>135157</v>
+        <v>137345</v>
       </c>
       <c r="D15" s="11">
-        <v>136015</v>
+        <v>144247</v>
       </c>
       <c r="E15" s="11">
-        <v>31442</v>
+        <v>34153</v>
       </c>
       <c r="F15" s="14">
         <v>33995</v>
       </c>
       <c r="G15" s="13">
-        <v>114495</v>
+        <v>121703</v>
       </c>
       <c r="H15" s="11">
-        <v>71626</v>
+        <v>73690</v>
       </c>
       <c r="I15" s="11">
-        <v>10623</v>
+        <v>10928</v>
       </c>
       <c r="J15" s="14">
-        <v>23552</v>
+        <v>23554</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
@@ -2813,28 +2818,28 @@
         <v>10</v>
       </c>
       <c r="C16" s="19">
-        <v>101323</v>
+        <v>105032</v>
       </c>
       <c r="D16" s="16">
-        <v>89795</v>
+        <v>92801</v>
       </c>
       <c r="E16" s="16">
-        <v>17892</v>
+        <v>18828</v>
       </c>
       <c r="F16" s="18">
-        <v>35672</v>
+        <v>35909</v>
       </c>
       <c r="G16" s="19">
-        <v>41912</v>
+        <v>42753</v>
       </c>
       <c r="H16" s="16">
-        <v>34999</v>
+        <v>35622</v>
       </c>
       <c r="I16" s="16">
-        <v>4442</v>
+        <v>4508</v>
       </c>
       <c r="J16" s="18">
-        <v>24536</v>
+        <v>24711</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
@@ -2845,28 +2850,28 @@
         <v>11</v>
       </c>
       <c r="C17" s="13">
-        <v>170128</v>
+        <v>179812</v>
       </c>
       <c r="D17" s="11">
-        <v>124231</v>
+        <v>127772</v>
       </c>
       <c r="E17" s="11">
-        <v>23276</v>
+        <v>26634</v>
       </c>
       <c r="F17" s="14">
-        <v>64284</v>
+        <v>64887</v>
       </c>
       <c r="G17" s="13">
-        <v>48498</v>
+        <v>50760</v>
       </c>
       <c r="H17" s="11">
-        <v>38568</v>
+        <v>38776</v>
       </c>
       <c r="I17" s="11">
-        <v>8982</v>
+        <v>8985</v>
       </c>
       <c r="J17" s="14">
-        <v>44317</v>
+        <v>44496</v>
       </c>
       <c r="K17" s="31"/>
     </row>
@@ -2878,28 +2883,28 @@
         <v>14</v>
       </c>
       <c r="C18" s="16">
-        <v>124508</v>
+        <v>132503</v>
       </c>
       <c r="D18" s="16">
-        <v>84917</v>
+        <v>87920</v>
       </c>
       <c r="E18" s="16">
-        <v>30694</v>
+        <v>35742</v>
       </c>
       <c r="F18" s="18">
-        <v>28835</v>
+        <v>29275</v>
       </c>
       <c r="G18" s="16">
-        <v>65355</v>
+        <v>65554</v>
       </c>
       <c r="H18" s="16">
-        <v>40607</v>
+        <v>40821</v>
       </c>
       <c r="I18" s="16">
-        <v>4612</v>
+        <v>4619</v>
       </c>
       <c r="J18" s="18">
-        <v>21438</v>
+        <v>21698</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -2938,28 +2943,28 @@
         <v>19</v>
       </c>
       <c r="C20" s="47">
-        <v>3882258</v>
+        <v>4076782</v>
       </c>
       <c r="D20" s="48">
-        <v>3683193</v>
+        <v>3853327</v>
       </c>
       <c r="E20" s="48">
-        <v>561664</v>
+        <v>621576</v>
       </c>
       <c r="F20" s="49">
-        <v>957152</v>
+        <v>954674</v>
       </c>
       <c r="G20" s="47">
-        <v>2023630</v>
+        <v>2154545</v>
       </c>
       <c r="H20" s="48">
-        <v>1352725</v>
+        <v>1361962</v>
       </c>
       <c r="I20" s="48">
-        <v>130695</v>
+        <v>137452</v>
       </c>
       <c r="J20" s="49">
-        <v>732379</v>
+        <v>732187</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
@@ -3040,13 +3045,13 @@
         <v>44192</v>
       </c>
       <c r="B2" s="32">
-        <v>23711</v>
+        <v>23904</v>
       </c>
       <c r="C2" s="32">
         <v>0</v>
       </c>
       <c r="D2" s="32">
-        <v>23711</v>
+        <v>23904</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -3054,13 +3059,13 @@
         <v>44193</v>
       </c>
       <c r="B3" s="32">
-        <v>18736</v>
+        <v>18750</v>
       </c>
       <c r="C3" s="32">
         <v>0</v>
       </c>
       <c r="D3" s="32">
-        <v>18736</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -3068,13 +3073,13 @@
         <v>44194</v>
       </c>
       <c r="B4" s="32">
-        <v>42819</v>
+        <v>48178</v>
       </c>
       <c r="C4" s="32">
         <v>0</v>
       </c>
       <c r="D4" s="32">
-        <v>42819</v>
+        <v>48178</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
@@ -3082,13 +3087,13 @@
         <v>44195</v>
       </c>
       <c r="B5" s="32">
-        <v>57993</v>
+        <v>62218</v>
       </c>
       <c r="C5" s="32">
         <v>0</v>
       </c>
       <c r="D5" s="32">
-        <v>57993</v>
+        <v>62218</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -3096,13 +3101,13 @@
         <v>44196</v>
       </c>
       <c r="B6" s="32">
-        <v>38866</v>
+        <v>47995</v>
       </c>
       <c r="C6" s="32">
         <v>0</v>
       </c>
       <c r="D6" s="32">
-        <v>38866</v>
+        <v>47995</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -3110,13 +3115,13 @@
         <v>44197</v>
       </c>
       <c r="B7" s="32">
-        <v>24666</v>
+        <v>19400</v>
       </c>
       <c r="C7" s="32">
         <v>0</v>
       </c>
       <c r="D7" s="32">
-        <v>24666</v>
+        <v>19400</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
@@ -3124,13 +3129,13 @@
         <v>44198</v>
       </c>
       <c r="B8" s="32">
-        <v>52188</v>
+        <v>52389</v>
       </c>
       <c r="C8" s="32">
         <v>0</v>
       </c>
       <c r="D8" s="32">
-        <v>52188</v>
+        <v>52389</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
@@ -3138,13 +3143,13 @@
         <v>44199</v>
       </c>
       <c r="B9" s="32">
-        <v>24989</v>
+        <v>24075</v>
       </c>
       <c r="C9" s="32">
         <v>0</v>
       </c>
       <c r="D9" s="32">
-        <v>24989</v>
+        <v>24075</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -3152,13 +3157,13 @@
         <v>44200</v>
       </c>
       <c r="B10" s="32">
-        <v>48714</v>
+        <v>48226</v>
       </c>
       <c r="C10" s="32">
         <v>0</v>
       </c>
       <c r="D10" s="32">
-        <v>48714</v>
+        <v>48226</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
@@ -3166,13 +3171,13 @@
         <v>44201</v>
       </c>
       <c r="B11" s="32">
-        <v>52389</v>
+        <v>53691</v>
       </c>
       <c r="C11" s="32">
         <v>0</v>
       </c>
       <c r="D11" s="32">
-        <v>52389</v>
+        <v>53691</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
@@ -3180,13 +3185,13 @@
         <v>44202</v>
       </c>
       <c r="B12" s="32">
-        <v>59357</v>
+        <v>62979</v>
       </c>
       <c r="C12" s="32">
         <v>0</v>
       </c>
       <c r="D12" s="32">
-        <v>59357</v>
+        <v>62979</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
@@ -3194,13 +3199,13 @@
         <v>44203</v>
       </c>
       <c r="B13" s="32">
-        <v>58410</v>
+        <v>55840</v>
       </c>
       <c r="C13" s="32">
         <v>0</v>
       </c>
       <c r="D13" s="32">
-        <v>58410</v>
+        <v>55840</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
@@ -3208,13 +3213,13 @@
         <v>44204</v>
       </c>
       <c r="B14" s="32">
-        <v>60855</v>
+        <v>63192</v>
       </c>
       <c r="C14" s="32">
         <v>0</v>
       </c>
       <c r="D14" s="32">
-        <v>60855</v>
+        <v>63192</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
@@ -3222,13 +3227,13 @@
         <v>44205</v>
       </c>
       <c r="B15" s="32">
-        <v>56984</v>
+        <v>60899</v>
       </c>
       <c r="C15" s="32">
         <v>0</v>
       </c>
       <c r="D15" s="32">
-        <v>56984</v>
+        <v>60899</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
@@ -3236,13 +3241,13 @@
         <v>44206</v>
       </c>
       <c r="B16" s="32">
-        <v>33460</v>
+        <v>34597</v>
       </c>
       <c r="C16" s="32">
         <v>0</v>
       </c>
       <c r="D16" s="32">
-        <v>33460</v>
+        <v>34597</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
@@ -3250,13 +3255,13 @@
         <v>44207</v>
       </c>
       <c r="B17" s="32">
-        <v>65972</v>
+        <v>65968</v>
       </c>
       <c r="C17" s="32">
         <v>0</v>
       </c>
       <c r="D17" s="32">
-        <v>65972</v>
+        <v>65968</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -3264,13 +3269,13 @@
         <v>44208</v>
       </c>
       <c r="B18" s="32">
-        <v>81818</v>
+        <v>82172</v>
       </c>
       <c r="C18" s="32">
         <v>0</v>
       </c>
       <c r="D18" s="32">
-        <v>81818</v>
+        <v>82172</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
@@ -3278,13 +3283,13 @@
         <v>44209</v>
       </c>
       <c r="B19" s="32">
-        <v>99284</v>
+        <v>110152</v>
       </c>
       <c r="C19" s="32">
         <v>0</v>
       </c>
       <c r="D19" s="32">
-        <v>99284</v>
+        <v>110152</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
@@ -3292,13 +3297,13 @@
         <v>44210</v>
       </c>
       <c r="B20" s="32">
-        <v>99903</v>
+        <v>82327</v>
       </c>
       <c r="C20" s="32">
         <v>114</v>
       </c>
       <c r="D20" s="32">
-        <v>100017</v>
+        <v>82441</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.45">
@@ -3306,13 +3311,13 @@
         <v>44211</v>
       </c>
       <c r="B21" s="32">
-        <v>92320</v>
+        <v>89483</v>
       </c>
       <c r="C21" s="32">
-        <v>431</v>
+        <v>709</v>
       </c>
       <c r="D21" s="32">
-        <v>92751</v>
+        <v>90192</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
@@ -3320,13 +3325,13 @@
         <v>44212</v>
       </c>
       <c r="B22" s="32">
-        <v>56753</v>
+        <v>56390</v>
       </c>
       <c r="C22" s="32">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="D22" s="32">
-        <v>57153</v>
+        <v>57385</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
@@ -3334,13 +3339,13 @@
         <v>44213</v>
       </c>
       <c r="B23" s="32">
-        <v>30692</v>
+        <v>30280</v>
       </c>
       <c r="C23" s="32">
-        <v>13694</v>
+        <v>16577</v>
       </c>
       <c r="D23" s="32">
-        <v>44386</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
@@ -3348,13 +3353,13 @@
         <v>44214</v>
       </c>
       <c r="B24" s="32">
-        <v>58100</v>
+        <v>64971</v>
       </c>
       <c r="C24" s="32">
-        <v>16370</v>
+        <v>15408</v>
       </c>
       <c r="D24" s="32">
-        <v>74470</v>
+        <v>80379</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
@@ -3362,13 +3367,13 @@
         <v>44215</v>
       </c>
       <c r="B25" s="32">
-        <v>68812</v>
+        <v>79480</v>
       </c>
       <c r="C25" s="32">
-        <v>27216</v>
+        <v>31561</v>
       </c>
       <c r="D25" s="32">
-        <v>96028</v>
+        <v>111041</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
@@ -3376,13 +3381,13 @@
         <v>44216</v>
       </c>
       <c r="B26" s="32">
-        <v>78625</v>
+        <v>79310</v>
       </c>
       <c r="C26" s="32">
-        <v>50796</v>
+        <v>50272</v>
       </c>
       <c r="D26" s="32">
-        <v>129421</v>
+        <v>129582</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
@@ -3390,13 +3395,13 @@
         <v>44217</v>
       </c>
       <c r="B27" s="32">
-        <v>61096</v>
+        <v>63851</v>
       </c>
       <c r="C27" s="32">
-        <v>35428</v>
+        <v>39067</v>
       </c>
       <c r="D27" s="32">
-        <v>96524</v>
+        <v>102918</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
@@ -3404,13 +3409,13 @@
         <v>44218</v>
       </c>
       <c r="B28" s="32">
-        <v>84468</v>
+        <v>67469</v>
       </c>
       <c r="C28" s="32">
-        <v>31393</v>
+        <v>34144</v>
       </c>
       <c r="D28" s="32">
-        <v>115861</v>
+        <v>101613</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
@@ -3418,13 +3423,13 @@
         <v>44219</v>
       </c>
       <c r="B29" s="32">
-        <v>49312</v>
+        <v>40781</v>
       </c>
       <c r="C29" s="32">
-        <v>43998</v>
+        <v>44445</v>
       </c>
       <c r="D29" s="32">
-        <v>93310</v>
+        <v>85226</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.45">
@@ -3432,13 +3437,13 @@
         <v>44220</v>
       </c>
       <c r="B30" s="32">
-        <v>38029</v>
+        <v>25423</v>
       </c>
       <c r="C30" s="32">
-        <v>28091</v>
+        <v>23739</v>
       </c>
       <c r="D30" s="32">
-        <v>66120</v>
+        <v>49162</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
@@ -3446,13 +3451,13 @@
         <v>44221</v>
       </c>
       <c r="B31" s="32">
-        <v>58212</v>
+        <v>58243</v>
       </c>
       <c r="C31" s="32">
-        <v>39692</v>
+        <v>37923</v>
       </c>
       <c r="D31" s="32">
-        <v>97904</v>
+        <v>96166</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
@@ -3460,13 +3465,13 @@
         <v>44222</v>
       </c>
       <c r="B32" s="32">
-        <v>53452</v>
+        <v>50862</v>
       </c>
       <c r="C32" s="32">
-        <v>49350</v>
+        <v>48549</v>
       </c>
       <c r="D32" s="32">
-        <v>102802</v>
+        <v>99411</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
@@ -3474,13 +3479,13 @@
         <v>44223</v>
       </c>
       <c r="B33" s="32">
-        <v>53805</v>
+        <v>51612</v>
       </c>
       <c r="C33" s="32">
-        <v>59385</v>
+        <v>59401</v>
       </c>
       <c r="D33" s="32">
-        <v>113190</v>
+        <v>111013</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
@@ -3488,13 +3493,13 @@
         <v>44224</v>
       </c>
       <c r="B34" s="32">
-        <v>51739</v>
+        <v>45086</v>
       </c>
       <c r="C34" s="32">
-        <v>48459</v>
+        <v>45814</v>
       </c>
       <c r="D34" s="32">
-        <v>100198</v>
+        <v>90900</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.45">
@@ -3502,13 +3507,13 @@
         <v>44225</v>
       </c>
       <c r="B35" s="32">
-        <v>55972</v>
+        <v>51425</v>
       </c>
       <c r="C35" s="32">
-        <v>53963</v>
+        <v>56227</v>
       </c>
       <c r="D35" s="32">
-        <v>109935</v>
+        <v>107652</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
@@ -3516,13 +3521,13 @@
         <v>44226</v>
       </c>
       <c r="B36" s="32">
-        <v>39452</v>
+        <v>35139</v>
       </c>
       <c r="C36" s="32">
-        <v>48554</v>
+        <v>50105</v>
       </c>
       <c r="D36" s="32">
-        <v>88006</v>
+        <v>85244</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
@@ -3530,13 +3535,13 @@
         <v>44227</v>
       </c>
       <c r="B37" s="32">
-        <v>31324</v>
+        <v>26408</v>
       </c>
       <c r="C37" s="32">
-        <v>31442</v>
+        <v>29877</v>
       </c>
       <c r="D37" s="32">
-        <v>62766</v>
+        <v>56285</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.45">
@@ -3544,13 +3549,13 @@
         <v>44228</v>
       </c>
       <c r="B38" s="32">
-        <v>50564</v>
+        <v>58009</v>
       </c>
       <c r="C38" s="32">
-        <v>65726</v>
+        <v>61467</v>
       </c>
       <c r="D38" s="32">
-        <v>116290</v>
+        <v>119476</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.45">
@@ -3558,13 +3563,13 @@
         <v>44229</v>
       </c>
       <c r="B39" s="32">
-        <v>58462</v>
+        <v>62021</v>
       </c>
       <c r="C39" s="32">
-        <v>69809</v>
+        <v>65959</v>
       </c>
       <c r="D39" s="32">
-        <v>128271</v>
+        <v>127980</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.45">
@@ -3572,13 +3577,13 @@
         <v>44230</v>
       </c>
       <c r="B40" s="32">
-        <v>58365</v>
+        <v>64128</v>
       </c>
       <c r="C40" s="32">
-        <v>85322</v>
+        <v>92481</v>
       </c>
       <c r="D40" s="32">
-        <v>143687</v>
+        <v>156609</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.45">
@@ -3586,13 +3591,13 @@
         <v>44231</v>
       </c>
       <c r="B41" s="32">
-        <v>63792</v>
+        <v>60139</v>
       </c>
       <c r="C41" s="32">
-        <v>72986</v>
+        <v>69380</v>
       </c>
       <c r="D41" s="32">
-        <v>136778</v>
+        <v>129519</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.45">
@@ -3600,13 +3605,13 @@
         <v>44232</v>
       </c>
       <c r="B42" s="32">
-        <v>60522</v>
+        <v>65141</v>
       </c>
       <c r="C42" s="32">
-        <v>74279</v>
+        <v>74452</v>
       </c>
       <c r="D42" s="32">
-        <v>134801</v>
+        <v>139593</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.45">
@@ -3614,13 +3619,13 @@
         <v>44233</v>
       </c>
       <c r="B43" s="32">
-        <v>49352</v>
+        <v>45476</v>
       </c>
       <c r="C43" s="32">
-        <v>55671</v>
+        <v>50693</v>
       </c>
       <c r="D43" s="32">
-        <v>105023</v>
+        <v>96169</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.45">
@@ -3628,13 +3633,13 @@
         <v>44234</v>
       </c>
       <c r="B44" s="32">
-        <v>33521</v>
+        <v>28036</v>
       </c>
       <c r="C44" s="32">
-        <v>26855</v>
+        <v>24969</v>
       </c>
       <c r="D44" s="32">
-        <v>60376</v>
+        <v>53005</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.45">
@@ -3642,13 +3647,13 @@
         <v>44235</v>
       </c>
       <c r="B45" s="32">
-        <v>54904</v>
+        <v>53296</v>
       </c>
       <c r="C45" s="32">
-        <v>52131</v>
+        <v>55370</v>
       </c>
       <c r="D45" s="32">
-        <v>107035</v>
+        <v>108666</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
@@ -3656,13 +3661,13 @@
         <v>44236</v>
       </c>
       <c r="B46" s="32">
-        <v>59865</v>
+        <v>59075</v>
       </c>
       <c r="C46" s="32">
-        <v>65842</v>
+        <v>71450</v>
       </c>
       <c r="D46" s="32">
-        <v>125707</v>
+        <v>130525</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.45">
@@ -3670,13 +3675,13 @@
         <v>44237</v>
       </c>
       <c r="B47" s="32">
-        <v>75549</v>
+        <v>72844</v>
       </c>
       <c r="C47" s="32">
-        <v>77978</v>
+        <v>75940</v>
       </c>
       <c r="D47" s="32">
-        <v>153527</v>
+        <v>148784</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -3684,13 +3689,13 @@
         <v>44238</v>
       </c>
       <c r="B48" s="32">
-        <v>71751</v>
+        <v>73137</v>
       </c>
       <c r="C48" s="32">
-        <v>72090</v>
+        <v>67669</v>
       </c>
       <c r="D48" s="32">
-        <v>143841</v>
+        <v>140806</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -3698,13 +3703,13 @@
         <v>44239</v>
       </c>
       <c r="B49" s="32">
-        <v>80427</v>
+        <v>79177</v>
       </c>
       <c r="C49" s="32">
-        <v>78830</v>
+        <v>75536</v>
       </c>
       <c r="D49" s="32">
-        <v>159257</v>
+        <v>154713</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
@@ -3712,13 +3717,13 @@
         <v>44240</v>
       </c>
       <c r="B50" s="32">
-        <v>63775</v>
+        <v>61707</v>
       </c>
       <c r="C50" s="32">
-        <v>47139</v>
+        <v>45854</v>
       </c>
       <c r="D50" s="32">
-        <v>110914</v>
+        <v>107561</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.45">
@@ -3726,13 +3731,13 @@
         <v>44241</v>
       </c>
       <c r="B51" s="32">
-        <v>39812</v>
+        <v>39690</v>
       </c>
       <c r="C51" s="32">
-        <v>26609</v>
+        <v>24995</v>
       </c>
       <c r="D51" s="32">
-        <v>66421</v>
+        <v>64685</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.45">
@@ -3740,13 +3745,13 @@
         <v>44242</v>
       </c>
       <c r="B52" s="32">
-        <v>70888</v>
+        <v>69741</v>
       </c>
       <c r="C52" s="32">
-        <v>56114</v>
+        <v>55467</v>
       </c>
       <c r="D52" s="32">
-        <v>127002</v>
+        <v>125208</v>
       </c>
     </row>
     <row r="53" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3754,13 +3759,13 @@
         <v>44243</v>
       </c>
       <c r="B53" s="32">
-        <v>81623</v>
+        <v>81184</v>
       </c>
       <c r="C53" s="32">
-        <v>53987</v>
+        <v>52775</v>
       </c>
       <c r="D53" s="32">
-        <v>135610</v>
+        <v>133959</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3768,13 +3773,13 @@
         <v>44244</v>
       </c>
       <c r="B54" s="32">
-        <v>95653</v>
+        <v>94089</v>
       </c>
       <c r="C54" s="32">
-        <v>54742</v>
+        <v>55051</v>
       </c>
       <c r="D54" s="32">
-        <v>150395</v>
+        <v>149140</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -3782,13 +3787,13 @@
         <v>44245</v>
       </c>
       <c r="B55" s="32">
-        <v>93953</v>
+        <v>91800</v>
       </c>
       <c r="C55" s="32">
-        <v>52816</v>
+        <v>51283</v>
       </c>
       <c r="D55" s="32">
-        <v>146769</v>
+        <v>143083</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3796,13 +3801,13 @@
         <v>44246</v>
       </c>
       <c r="B56" s="32">
-        <v>98233</v>
+        <v>98589</v>
       </c>
       <c r="C56" s="32">
-        <v>53326</v>
+        <v>52829</v>
       </c>
       <c r="D56" s="32">
-        <v>151559</v>
+        <v>151418</v>
       </c>
     </row>
     <row r="57" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3810,13 +3815,13 @@
         <v>44247</v>
       </c>
       <c r="B57" s="32">
-        <v>75413</v>
+        <v>76289</v>
       </c>
       <c r="C57" s="32">
-        <v>37672</v>
+        <v>37548</v>
       </c>
       <c r="D57" s="32">
-        <v>113085</v>
+        <v>113837</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3824,13 +3829,13 @@
         <v>44248</v>
       </c>
       <c r="B58" s="32">
-        <v>56544</v>
+        <v>56792</v>
       </c>
       <c r="C58" s="32">
-        <v>29067</v>
+        <v>28686</v>
       </c>
       <c r="D58" s="32">
-        <v>85611</v>
+        <v>85478</v>
       </c>
     </row>
     <row r="59" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3838,13 +3843,13 @@
         <v>44249</v>
       </c>
       <c r="B59" s="32">
-        <v>99832</v>
+        <v>99219</v>
       </c>
       <c r="C59" s="32">
-        <v>53111</v>
+        <v>59795</v>
       </c>
       <c r="D59" s="32">
-        <v>152943</v>
+        <v>159014</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3852,13 +3857,13 @@
         <v>44250</v>
       </c>
       <c r="B60" s="32">
-        <v>105014</v>
+        <v>105878</v>
       </c>
       <c r="C60" s="32">
-        <v>56601</v>
+        <v>58281</v>
       </c>
       <c r="D60" s="32">
-        <v>161615</v>
+        <v>164159</v>
       </c>
     </row>
     <row r="61" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3866,13 +3871,13 @@
         <v>44251</v>
       </c>
       <c r="B61" s="32">
-        <v>115132</v>
+        <v>115238</v>
       </c>
       <c r="C61" s="32">
-        <v>58152</v>
+        <v>58150</v>
       </c>
       <c r="D61" s="32">
-        <v>173284</v>
+        <v>173388</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3880,13 +3885,13 @@
         <v>44252</v>
       </c>
       <c r="B62" s="32">
-        <v>127762</v>
+        <v>128770</v>
       </c>
       <c r="C62" s="32">
-        <v>53242</v>
+        <v>56291</v>
       </c>
       <c r="D62" s="32">
-        <v>181004</v>
+        <v>185061</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3894,13 +3899,13 @@
         <v>44253</v>
       </c>
       <c r="B63" s="32">
-        <v>137589</v>
+        <v>141483</v>
       </c>
       <c r="C63" s="32">
-        <v>59471</v>
+        <v>62052</v>
       </c>
       <c r="D63" s="32">
-        <v>197060</v>
+        <v>203535</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3908,13 +3913,13 @@
         <v>44254</v>
       </c>
       <c r="B64" s="32">
-        <v>109182</v>
+        <v>110325</v>
       </c>
       <c r="C64" s="32">
-        <v>38820</v>
+        <v>39241</v>
       </c>
       <c r="D64" s="32">
-        <v>148002</v>
+        <v>149566</v>
       </c>
     </row>
     <row r="65" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -3922,13 +3927,13 @@
         <v>44255</v>
       </c>
       <c r="B65" s="32">
-        <v>84513</v>
+        <v>83533</v>
       </c>
       <c r="C65" s="32">
-        <v>28164</v>
+        <v>24138</v>
       </c>
       <c r="D65" s="32">
-        <v>112677</v>
+        <v>107671</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
@@ -3936,13 +3941,13 @@
         <v>44256</v>
       </c>
       <c r="B66" s="32">
-        <v>141670</v>
+        <v>143140</v>
       </c>
       <c r="C66" s="32">
-        <v>50461</v>
+        <v>48702</v>
       </c>
       <c r="D66" s="32">
-        <v>192131</v>
+        <v>191842</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
@@ -3950,13 +3955,13 @@
         <v>44257</v>
       </c>
       <c r="B67" s="32">
-        <v>162224</v>
+        <v>163171</v>
       </c>
       <c r="C67" s="32">
-        <v>55920</v>
+        <v>52777</v>
       </c>
       <c r="D67" s="32">
-        <v>218144</v>
+        <v>215948</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
@@ -3964,13 +3969,13 @@
         <v>44258</v>
       </c>
       <c r="B68" s="32">
-        <v>174543</v>
+        <v>171370</v>
       </c>
       <c r="C68" s="32">
-        <v>67813</v>
+        <v>66919</v>
       </c>
       <c r="D68" s="32">
-        <v>242356</v>
+        <v>238289</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
@@ -3978,13 +3983,13 @@
         <v>44259</v>
       </c>
       <c r="B69" s="32">
-        <v>177875</v>
+        <v>176745</v>
       </c>
       <c r="C69" s="32">
-        <v>62937</v>
+        <v>61575</v>
       </c>
       <c r="D69" s="32">
-        <v>240812</v>
+        <v>238320</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
@@ -3992,13 +3997,13 @@
         <v>44260</v>
       </c>
       <c r="B70" s="32">
-        <v>188911</v>
+        <v>194706</v>
       </c>
       <c r="C70" s="32">
-        <v>63516</v>
+        <v>65506</v>
       </c>
       <c r="D70" s="32">
-        <v>252427</v>
+        <v>260212</v>
       </c>
     </row>
     <row r="71" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4006,13 +4011,13 @@
         <v>44261</v>
       </c>
       <c r="B71" s="32">
-        <v>146857</v>
+        <v>152034</v>
       </c>
       <c r="C71" s="32">
-        <v>47345</v>
+        <v>48803</v>
       </c>
       <c r="D71" s="32">
-        <v>194202</v>
+        <v>200837</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4020,13 +4025,13 @@
         <v>44262</v>
       </c>
       <c r="B72" s="32">
-        <v>113743</v>
+        <v>116918</v>
       </c>
       <c r="C72" s="32">
-        <v>34532</v>
+        <v>34972</v>
       </c>
       <c r="D72" s="32">
-        <v>148275</v>
+        <v>151890</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4034,13 +4039,13 @@
         <v>44263</v>
       </c>
       <c r="B73" s="50">
-        <v>178545</v>
+        <v>182670</v>
       </c>
       <c r="C73" s="50">
-        <v>53456</v>
+        <v>52034</v>
       </c>
       <c r="D73" s="50">
-        <v>232001</v>
+        <v>234704</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4048,13 +4053,13 @@
         <v>44264</v>
       </c>
       <c r="B74" s="50">
-        <v>193222</v>
+        <v>192661</v>
       </c>
       <c r="C74" s="50">
-        <v>55118</v>
+        <v>54515</v>
       </c>
       <c r="D74" s="50">
-        <v>248340</v>
+        <v>247176</v>
       </c>
     </row>
     <row r="75" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4062,13 +4067,13 @@
         <v>44265</v>
       </c>
       <c r="B75" s="50">
-        <v>213010</v>
+        <v>216760</v>
       </c>
       <c r="C75" s="50">
-        <v>67701</v>
+        <v>65555</v>
       </c>
       <c r="D75" s="50">
-        <v>280711</v>
+        <v>282315</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4076,13 +4081,13 @@
         <v>44266</v>
       </c>
       <c r="B76" s="50">
-        <v>226876</v>
+        <v>225005</v>
       </c>
       <c r="C76" s="50">
-        <v>62993</v>
+        <v>62025</v>
       </c>
       <c r="D76" s="50">
-        <v>289869</v>
+        <v>287030</v>
       </c>
     </row>
     <row r="77" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4090,13 +4095,13 @@
         <v>44267</v>
       </c>
       <c r="B77" s="50">
-        <v>236391</v>
+        <v>243097</v>
       </c>
       <c r="C77" s="50">
-        <v>69437</v>
+        <v>70827</v>
       </c>
       <c r="D77" s="50">
-        <v>305828</v>
+        <v>313924</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4104,13 +4109,13 @@
         <v>44268</v>
       </c>
       <c r="B78" s="50">
-        <v>189444</v>
+        <v>194577</v>
       </c>
       <c r="C78" s="50">
-        <v>48254</v>
+        <v>49135</v>
       </c>
       <c r="D78" s="50">
-        <v>237698</v>
+        <v>243712</v>
       </c>
     </row>
     <row r="79" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4118,13 +4123,13 @@
         <v>44269</v>
       </c>
       <c r="B79" s="50">
-        <v>130704</v>
+        <v>133476</v>
       </c>
       <c r="C79" s="50">
-        <v>35241</v>
+        <v>35870</v>
       </c>
       <c r="D79" s="50">
-        <v>165945</v>
+        <v>169346</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4132,13 +4137,13 @@
         <v>44270</v>
       </c>
       <c r="B80" s="50">
-        <v>177391</v>
+        <v>186389</v>
       </c>
       <c r="C80" s="50">
-        <v>57409</v>
+        <v>58397</v>
       </c>
       <c r="D80" s="50">
-        <v>234800</v>
+        <v>244786</v>
       </c>
     </row>
     <row r="81" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4146,13 +4151,13 @@
         <v>44271</v>
       </c>
       <c r="B81" s="50">
-        <v>111687</v>
+        <v>112457</v>
       </c>
       <c r="C81" s="50">
-        <v>66382</v>
+        <v>66833</v>
       </c>
       <c r="D81" s="50">
-        <v>178069</v>
+        <v>179290</v>
       </c>
     </row>
     <row r="82" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4160,13 +4165,13 @@
         <v>44272</v>
       </c>
       <c r="B82" s="50">
-        <v>127894</v>
+        <v>129586</v>
       </c>
       <c r="C82" s="50">
-        <v>81441</v>
+        <v>82344</v>
       </c>
       <c r="D82" s="50">
-        <v>209335</v>
+        <v>211930</v>
       </c>
     </row>
     <row r="83" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4174,13 +4179,13 @@
         <v>44273</v>
       </c>
       <c r="B83" s="50">
-        <v>116160</v>
+        <v>117435</v>
       </c>
       <c r="C83" s="50">
-        <v>73499</v>
+        <v>73907</v>
       </c>
       <c r="D83" s="50">
-        <v>189659</v>
+        <v>191342</v>
       </c>
     </row>
     <row r="84" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4188,13 +4193,13 @@
         <v>44274</v>
       </c>
       <c r="B84" s="50">
-        <v>150219</v>
+        <v>155943</v>
       </c>
       <c r="C84" s="50">
-        <v>80367</v>
+        <v>81728</v>
       </c>
       <c r="D84" s="50">
-        <v>230586</v>
+        <v>237671</v>
       </c>
     </row>
     <row r="85" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4202,13 +4207,13 @@
         <v>44275</v>
       </c>
       <c r="B85" s="50">
-        <v>155715</v>
+        <v>161806</v>
       </c>
       <c r="C85" s="50">
-        <v>52985</v>
+        <v>53508</v>
       </c>
       <c r="D85" s="50">
-        <v>208700</v>
+        <v>215314</v>
       </c>
     </row>
     <row r="86" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4216,13 +4221,13 @@
         <v>44276</v>
       </c>
       <c r="B86" s="50">
-        <v>125667</v>
+        <v>128695</v>
       </c>
       <c r="C86" s="50">
-        <v>39164</v>
+        <v>39371</v>
       </c>
       <c r="D86" s="50">
-        <v>164831</v>
+        <v>168066</v>
       </c>
     </row>
     <row r="87" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4230,13 +4235,13 @@
         <v>44277</v>
       </c>
       <c r="B87" s="50">
-        <v>185387</v>
+        <v>190660</v>
       </c>
       <c r="C87" s="50">
-        <v>78180</v>
+        <v>79390</v>
       </c>
       <c r="D87" s="50">
-        <v>263567</v>
+        <v>270050</v>
       </c>
     </row>
     <row r="88" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4244,13 +4249,13 @@
         <v>44278</v>
       </c>
       <c r="B88" s="50">
-        <v>196651</v>
+        <v>201703</v>
       </c>
       <c r="C88" s="50">
-        <v>81808</v>
+        <v>82288</v>
       </c>
       <c r="D88" s="50">
-        <v>278459</v>
+        <v>283991</v>
       </c>
     </row>
     <row r="89" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4258,13 +4263,13 @@
         <v>44279</v>
       </c>
       <c r="B89" s="50">
-        <v>209045</v>
+        <v>214579</v>
       </c>
       <c r="C89" s="50">
-        <v>85761</v>
+        <v>86507</v>
       </c>
       <c r="D89" s="50">
-        <v>294806</v>
+        <v>301086</v>
       </c>
     </row>
     <row r="90" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4272,13 +4277,13 @@
         <v>44280</v>
       </c>
       <c r="B90" s="50">
-        <v>222670</v>
+        <v>225748</v>
       </c>
       <c r="C90" s="50">
-        <v>77990</v>
+        <v>78218</v>
       </c>
       <c r="D90" s="50">
-        <v>300660</v>
+        <v>303966</v>
       </c>
     </row>
     <row r="91" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
@@ -4286,26 +4291,42 @@
         <v>44281</v>
       </c>
       <c r="B91" s="50">
-        <v>207609</v>
+        <v>223520</v>
       </c>
       <c r="C91" s="50">
-        <v>83022</v>
+        <v>85490</v>
       </c>
       <c r="D91" s="50">
-        <v>290631</v>
+        <v>309010</v>
       </c>
     </row>
     <row r="92" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="51"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
+      <c r="A92" s="37">
+        <v>44282</v>
+      </c>
+      <c r="B92" s="50">
+        <v>208973</v>
+      </c>
+      <c r="C92" s="50">
+        <v>63447</v>
+      </c>
+      <c r="D92" s="50">
+        <v>272420</v>
+      </c>
     </row>
     <row r="93" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A93" s="51"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
+      <c r="A93" s="37">
+        <v>44283</v>
+      </c>
+      <c r="B93" s="50">
+        <v>123170</v>
+      </c>
+      <c r="C93" s="50">
+        <v>44522</v>
+      </c>
+      <c r="D93" s="50">
+        <v>167692</v>
+      </c>
     </row>
     <row r="94" spans="1:4" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A94" s="51"/>
@@ -4331,15 +4352,15 @@
       </c>
       <c r="B97" s="32">
         <f>SUM(B2:B96)</f>
-        <v>8595379</v>
+        <v>8994965</v>
       </c>
       <c r="C97" s="32">
         <f t="shared" ref="C97" si="0">SUM(C2:C96)</f>
-        <v>3768060</v>
+        <v>3877894</v>
       </c>
       <c r="D97" s="32">
         <f>SUM(D2:D96)</f>
-        <v>12363439</v>
+        <v>12872859</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.45">
@@ -4363,15 +4384,15 @@
       </c>
       <c r="B99" s="59">
         <f>B97+B98</f>
-        <v>8602339</v>
+        <v>9001925</v>
       </c>
       <c r="C99" s="59">
         <f>C97+C98</f>
-        <v>3768080</v>
+        <v>3877914</v>
       </c>
       <c r="D99" s="59">
         <f>D97+D98</f>
-        <v>12370419</v>
+        <v>12879839</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.45">
